--- a/mlp-exp/alpha_sweep_results.xlsx
+++ b/mlp-exp/alpha_sweep_results.xlsx
@@ -399,19 +399,19 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>27</v>
+        <v>21.5</v>
       </c>
       <c r="D2">
-        <v>66.8</v>
+        <v>57.2</v>
       </c>
       <c r="E2">
-        <v>95.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="F2">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="G2">
         <v>100</v>
@@ -425,25 +425,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>41.7</v>
+        <v>44.3</v>
       </c>
       <c r="C3">
-        <v>44.5</v>
+        <v>45.9</v>
       </c>
       <c r="D3">
-        <v>47</v>
+        <v>47.3</v>
       </c>
       <c r="E3">
-        <v>52.2</v>
+        <v>49.1</v>
       </c>
       <c r="F3">
-        <v>62.2</v>
+        <v>53.5</v>
       </c>
       <c r="G3">
-        <v>77.40000000000001</v>
+        <v>62</v>
       </c>
       <c r="H3">
-        <v>94.89999999999999</v>
+        <v>75.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -451,25 +451,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>40.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="C4">
-        <v>40.7</v>
+        <v>50</v>
       </c>
       <c r="D4">
-        <v>41.2</v>
+        <v>50</v>
       </c>
       <c r="E4">
-        <v>41.8</v>
+        <v>50</v>
       </c>
       <c r="F4">
-        <v>42.7</v>
+        <v>50</v>
       </c>
       <c r="G4">
-        <v>44.1</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>51.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -477,19 +477,19 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="C5">
-        <v>24.8</v>
+        <v>26.2</v>
       </c>
       <c r="D5">
-        <v>47.3</v>
+        <v>48.1</v>
       </c>
       <c r="E5">
-        <v>77.5</v>
+        <v>81.8</v>
       </c>
       <c r="F5">
-        <v>99.8</v>
+        <v>99.5</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -554,25 +554,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>8</v>
+        <v>7.000000000000001</v>
       </c>
       <c r="C2">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="D2">
-        <v>11.2</v>
+        <v>14.7</v>
       </c>
       <c r="E2">
-        <v>18.6</v>
+        <v>24.5</v>
       </c>
       <c r="F2">
-        <v>35.6</v>
+        <v>38.2</v>
       </c>
       <c r="G2">
-        <v>52.1</v>
+        <v>46.3</v>
       </c>
       <c r="H2">
-        <v>47.5</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -580,25 +580,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>48</v>
+        <v>48.7</v>
       </c>
       <c r="C3">
-        <v>47.2</v>
+        <v>48.4</v>
       </c>
       <c r="D3">
-        <v>47.09999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="E3">
-        <v>48.5</v>
+        <v>49.7</v>
       </c>
       <c r="F3">
-        <v>48</v>
+        <v>48.8</v>
       </c>
       <c r="G3">
-        <v>49.9</v>
+        <v>50.9</v>
       </c>
       <c r="H3">
-        <v>51.4</v>
+        <v>50.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -606,25 +606,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>49.2</v>
+        <v>51</v>
       </c>
       <c r="C4">
-        <v>49.1</v>
+        <v>52.6</v>
       </c>
       <c r="D4">
-        <v>48.2</v>
+        <v>52.2</v>
       </c>
       <c r="E4">
-        <v>48.8</v>
+        <v>51.3</v>
       </c>
       <c r="F4">
-        <v>46.9</v>
+        <v>47.59999999999999</v>
       </c>
       <c r="G4">
-        <v>48.7</v>
+        <v>55.3</v>
       </c>
       <c r="H4">
-        <v>50.6</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -632,25 +632,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="C5">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>26.1</v>
       </c>
       <c r="E5">
-        <v>28.3</v>
+        <v>32.9</v>
       </c>
       <c r="F5">
-        <v>38.1</v>
+        <v>41.6</v>
       </c>
       <c r="G5">
-        <v>48.9</v>
+        <v>47.7</v>
       </c>
       <c r="H5">
-        <v>51.7</v>
+        <v>50.1</v>
       </c>
     </row>
   </sheetData>
@@ -709,25 +709,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>17.8</v>
+        <v>12.7</v>
       </c>
       <c r="D2">
-        <v>31.8</v>
+        <v>23.4</v>
       </c>
       <c r="E2">
-        <v>45.7</v>
+        <v>45.5</v>
       </c>
       <c r="F2">
-        <v>47.09999999999999</v>
+        <v>54.2</v>
       </c>
       <c r="G2">
-        <v>52.6</v>
+        <v>51.8</v>
       </c>
       <c r="H2">
-        <v>49.4</v>
+        <v>48.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -735,25 +735,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>18.9</v>
+        <v>19.7</v>
       </c>
       <c r="C3">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="D3">
-        <v>25.1</v>
+        <v>22.8</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>23.1</v>
       </c>
       <c r="F3">
-        <v>32.8</v>
+        <v>26.2</v>
       </c>
       <c r="G3">
-        <v>37.4</v>
+        <v>28.6</v>
       </c>
       <c r="H3">
-        <v>45.2</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -761,25 +761,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>20.3</v>
+        <v>24.7</v>
       </c>
       <c r="C4">
-        <v>18.7</v>
+        <v>25.9</v>
       </c>
       <c r="D4">
-        <v>20.9</v>
+        <v>23.9</v>
       </c>
       <c r="E4">
-        <v>19.4</v>
+        <v>24.5</v>
       </c>
       <c r="F4">
-        <v>21.2</v>
+        <v>25.6</v>
       </c>
       <c r="G4">
-        <v>21</v>
+        <v>25.4</v>
       </c>
       <c r="H4">
-        <v>27.3</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -790,22 +790,22 @@
         <v>0.1</v>
       </c>
       <c r="C5">
-        <v>17.6</v>
+        <v>16.1</v>
       </c>
       <c r="D5">
-        <v>24.1</v>
+        <v>22.2</v>
       </c>
       <c r="E5">
-        <v>39.3</v>
+        <v>40.3</v>
       </c>
       <c r="F5">
-        <v>49.5</v>
+        <v>50.3</v>
       </c>
       <c r="G5">
-        <v>49.8</v>
+        <v>49.1</v>
       </c>
       <c r="H5">
-        <v>50.1</v>
+        <v>50.6</v>
       </c>
     </row>
   </sheetData>

--- a/mlp-exp/alpha_sweep_results.xlsx
+++ b/mlp-exp/alpha_sweep_results.xlsx
@@ -399,19 +399,19 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C2">
-        <v>21.5</v>
+        <v>35.5</v>
       </c>
       <c r="D2">
-        <v>57.2</v>
+        <v>75.3</v>
       </c>
       <c r="E2">
-        <v>90.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="F2">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>100</v>
@@ -425,25 +425,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>44.3</v>
+        <v>39.6</v>
       </c>
       <c r="C3">
-        <v>45.9</v>
+        <v>40.5</v>
       </c>
       <c r="D3">
-        <v>47.3</v>
+        <v>41.5</v>
       </c>
       <c r="E3">
-        <v>49.1</v>
+        <v>43.5</v>
       </c>
       <c r="F3">
-        <v>53.5</v>
+        <v>46.1</v>
       </c>
       <c r="G3">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H3">
-        <v>75.7</v>
+        <v>69.19999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -477,19 +477,19 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="C5">
-        <v>26.2</v>
+        <v>32.4</v>
       </c>
       <c r="D5">
-        <v>48.1</v>
+        <v>54.7</v>
       </c>
       <c r="E5">
-        <v>81.8</v>
+        <v>84.7</v>
       </c>
       <c r="F5">
-        <v>99.5</v>
+        <v>98.5</v>
       </c>
       <c r="G5">
         <v>100</v>
@@ -554,25 +554,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>7.000000000000001</v>
+        <v>22.8</v>
       </c>
       <c r="C2">
-        <v>9</v>
+        <v>30.5</v>
       </c>
       <c r="D2">
-        <v>14.7</v>
+        <v>44.1</v>
       </c>
       <c r="E2">
-        <v>24.5</v>
+        <v>52.90000000000001</v>
       </c>
       <c r="F2">
-        <v>38.2</v>
+        <v>44.2</v>
       </c>
       <c r="G2">
-        <v>46.3</v>
+        <v>47.8</v>
       </c>
       <c r="H2">
-        <v>51.5</v>
+        <v>49.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -580,25 +580,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>48.7</v>
+        <v>52.3</v>
       </c>
       <c r="C3">
-        <v>48.4</v>
+        <v>49.6</v>
       </c>
       <c r="D3">
-        <v>48.8</v>
+        <v>49.4</v>
       </c>
       <c r="E3">
-        <v>49.7</v>
+        <v>50.6</v>
       </c>
       <c r="F3">
-        <v>48.8</v>
+        <v>52.8</v>
       </c>
       <c r="G3">
-        <v>50.9</v>
+        <v>53</v>
       </c>
       <c r="H3">
-        <v>50.1</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -606,25 +606,25 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>50.6</v>
+      </c>
+      <c r="C4">
+        <v>48.9</v>
+      </c>
+      <c r="D4">
+        <v>49.6</v>
+      </c>
+      <c r="E4">
         <v>51</v>
       </c>
-      <c r="C4">
-        <v>52.6</v>
-      </c>
-      <c r="D4">
-        <v>52.2</v>
-      </c>
-      <c r="E4">
-        <v>51.3</v>
-      </c>
       <c r="F4">
-        <v>47.59999999999999</v>
+        <v>52.90000000000001</v>
       </c>
       <c r="G4">
-        <v>55.3</v>
+        <v>50.4</v>
       </c>
       <c r="H4">
-        <v>52.5</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -632,25 +632,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>24</v>
+        <v>29.9</v>
       </c>
       <c r="C5">
-        <v>24</v>
+        <v>32.9</v>
       </c>
       <c r="D5">
-        <v>26.1</v>
+        <v>43.2</v>
       </c>
       <c r="E5">
-        <v>32.9</v>
+        <v>54.90000000000001</v>
       </c>
       <c r="F5">
-        <v>41.6</v>
+        <v>46.3</v>
       </c>
       <c r="G5">
-        <v>47.7</v>
+        <v>49.4</v>
       </c>
       <c r="H5">
-        <v>50.1</v>
+        <v>51.7</v>
       </c>
     </row>
   </sheetData>
@@ -709,25 +709,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="C2">
-        <v>12.7</v>
+        <v>15.3</v>
       </c>
       <c r="D2">
-        <v>23.4</v>
+        <v>35.09999999999999</v>
       </c>
       <c r="E2">
-        <v>45.5</v>
+        <v>41.9</v>
       </c>
       <c r="F2">
-        <v>54.2</v>
+        <v>53</v>
       </c>
       <c r="G2">
-        <v>51.8</v>
+        <v>51</v>
       </c>
       <c r="H2">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -735,25 +735,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>19.7</v>
+        <v>21.5</v>
       </c>
       <c r="C3">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="D3">
-        <v>22.8</v>
+        <v>20.3</v>
       </c>
       <c r="E3">
-        <v>23.1</v>
+        <v>22.4</v>
       </c>
       <c r="F3">
-        <v>26.2</v>
+        <v>24.7</v>
       </c>
       <c r="G3">
-        <v>28.6</v>
+        <v>27</v>
       </c>
       <c r="H3">
-        <v>35.5</v>
+        <v>33.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -761,25 +761,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>24.7</v>
+        <v>24.2</v>
       </c>
       <c r="C4">
+        <v>25.8</v>
+      </c>
+      <c r="D4">
         <v>25.9</v>
       </c>
-      <c r="D4">
-        <v>23.9</v>
-      </c>
       <c r="E4">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="F4">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="G4">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="H4">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -787,25 +787,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="C5">
-        <v>16.1</v>
+        <v>14.1</v>
       </c>
       <c r="D5">
-        <v>22.2</v>
+        <v>25.2</v>
       </c>
       <c r="E5">
-        <v>40.3</v>
+        <v>39.3</v>
       </c>
       <c r="F5">
-        <v>50.3</v>
+        <v>50.9</v>
       </c>
       <c r="G5">
-        <v>49.1</v>
+        <v>51.2</v>
       </c>
       <c r="H5">
-        <v>50.6</v>
+        <v>49.6</v>
       </c>
     </row>
   </sheetData>

--- a/mlp-exp/alpha_sweep_results.xlsx
+++ b/mlp-exp/alpha_sweep_results.xlsx
@@ -362,13 +362,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="8" width="4.7109375" customWidth="1"/>
+    <col min="2" max="16" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -393,113 +393,233 @@
       <c r="H1">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1">
+        <v>20</v>
+      </c>
+      <c r="J1">
+        <v>32</v>
+      </c>
+      <c r="K1">
+        <v>64</v>
+      </c>
+      <c r="L1">
+        <v>100</v>
+      </c>
+      <c r="M1">
+        <v>128</v>
+      </c>
+      <c r="N1">
+        <v>256</v>
+      </c>
+      <c r="O1">
+        <v>512</v>
+      </c>
+      <c r="P1">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>35.5</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>75.3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>11.9</v>
+      </c>
+      <c r="L2">
+        <v>32.4</v>
+      </c>
+      <c r="M2">
+        <v>44</v>
+      </c>
+      <c r="N2">
+        <v>89.8</v>
+      </c>
+      <c r="O2">
         <v>100</v>
       </c>
-      <c r="G2">
+      <c r="P2">
         <v>100</v>
       </c>
-      <c r="H2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>39.6</v>
+        <v>21.2</v>
       </c>
       <c r="C3">
-        <v>40.5</v>
+        <v>21.2</v>
       </c>
       <c r="D3">
-        <v>41.5</v>
+        <v>21.3</v>
       </c>
       <c r="E3">
-        <v>43.5</v>
+        <v>21.3</v>
       </c>
       <c r="F3">
-        <v>46.1</v>
+        <v>21.3</v>
       </c>
       <c r="G3">
-        <v>54</v>
+        <v>21.5</v>
       </c>
       <c r="H3">
-        <v>69.19999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>22.1</v>
+      </c>
+      <c r="I3">
+        <v>22.4</v>
+      </c>
+      <c r="J3">
+        <v>23.6</v>
+      </c>
+      <c r="K3">
+        <v>28.7</v>
+      </c>
+      <c r="L3">
+        <v>32.5</v>
+      </c>
+      <c r="M3">
+        <v>36.8</v>
+      </c>
+      <c r="N3">
+        <v>54.50000000000001</v>
+      </c>
+      <c r="O3">
+        <v>81.5</v>
+      </c>
+      <c r="P3">
+        <v>99.40000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="C4">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="D4">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="E4">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="F4">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>50.7</v>
       </c>
       <c r="H4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>50.7</v>
+      </c>
+      <c r="I4">
+        <v>50.7</v>
+      </c>
+      <c r="J4">
+        <v>50.7</v>
+      </c>
+      <c r="K4">
+        <v>50.9</v>
+      </c>
+      <c r="L4">
+        <v>50.9</v>
+      </c>
+      <c r="M4">
+        <v>51</v>
+      </c>
+      <c r="N4">
+        <v>51.8</v>
+      </c>
+      <c r="O4">
+        <v>53.5</v>
+      </c>
+      <c r="P4">
+        <v>56.8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="C5">
-        <v>32.4</v>
+        <v>1.2</v>
       </c>
       <c r="D5">
-        <v>54.7</v>
+        <v>1.2</v>
       </c>
       <c r="E5">
-        <v>84.7</v>
+        <v>1.2</v>
       </c>
       <c r="F5">
-        <v>98.5</v>
+        <v>1.5</v>
       </c>
       <c r="G5">
+        <v>2.9</v>
+      </c>
+      <c r="H5">
+        <v>4.2</v>
+      </c>
+      <c r="I5">
+        <v>5.4</v>
+      </c>
+      <c r="J5">
+        <v>8.1</v>
+      </c>
+      <c r="K5">
+        <v>16.1</v>
+      </c>
+      <c r="L5">
+        <v>26.1</v>
+      </c>
+      <c r="M5">
+        <v>33.2</v>
+      </c>
+      <c r="N5">
+        <v>59.5</v>
+      </c>
+      <c r="O5">
+        <v>91.60000000000001</v>
+      </c>
+      <c r="P5">
         <v>100</v>
       </c>
-      <c r="H5">
-        <v>100</v>
-      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:H5">
+  <conditionalFormatting sqref="B2:P5">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -517,13 +637,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="8" width="4.7109375" customWidth="1"/>
+    <col min="2" max="16" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -548,113 +668,233 @@
       <c r="H1">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1">
+        <v>20</v>
+      </c>
+      <c r="J1">
+        <v>32</v>
+      </c>
+      <c r="K1">
+        <v>64</v>
+      </c>
+      <c r="L1">
+        <v>100</v>
+      </c>
+      <c r="M1">
+        <v>128</v>
+      </c>
+      <c r="N1">
+        <v>256</v>
+      </c>
+      <c r="O1">
+        <v>512</v>
+      </c>
+      <c r="P1">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>22.8</v>
+        <v>0.5</v>
       </c>
       <c r="C2">
-        <v>30.5</v>
+        <v>0.5</v>
       </c>
       <c r="D2">
-        <v>44.1</v>
+        <v>0.5</v>
       </c>
       <c r="E2">
-        <v>52.90000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="F2">
-        <v>44.2</v>
+        <v>0.5</v>
       </c>
       <c r="G2">
-        <v>47.8</v>
+        <v>0.6</v>
       </c>
       <c r="H2">
-        <v>49.8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="I2">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="J2">
+        <v>1.7</v>
+      </c>
+      <c r="K2">
+        <v>7.9</v>
+      </c>
+      <c r="L2">
+        <v>21.3</v>
+      </c>
+      <c r="M2">
+        <v>31.9</v>
+      </c>
+      <c r="N2">
+        <v>50</v>
+      </c>
+      <c r="O2">
+        <v>46.5</v>
+      </c>
+      <c r="P2">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>52.3</v>
+        <v>49.7</v>
       </c>
       <c r="C3">
         <v>49.6</v>
       </c>
       <c r="D3">
-        <v>49.4</v>
+        <v>49.7</v>
       </c>
       <c r="E3">
+        <v>49.7</v>
+      </c>
+      <c r="F3">
+        <v>50</v>
+      </c>
+      <c r="G3">
+        <v>50.1</v>
+      </c>
+      <c r="H3">
+        <v>50.7</v>
+      </c>
+      <c r="I3">
         <v>50.6</v>
       </c>
-      <c r="F3">
+      <c r="J3">
+        <v>51.2</v>
+      </c>
+      <c r="K3">
+        <v>51.3</v>
+      </c>
+      <c r="L3">
+        <v>53.3</v>
+      </c>
+      <c r="M3">
+        <v>53.1</v>
+      </c>
+      <c r="N3">
+        <v>53</v>
+      </c>
+      <c r="O3">
+        <v>53.3</v>
+      </c>
+      <c r="P3">
         <v>52.8</v>
       </c>
-      <c r="G3">
-        <v>53</v>
-      </c>
-      <c r="H3">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>50.6</v>
+        <v>49.8</v>
       </c>
       <c r="C4">
+        <v>49.8</v>
+      </c>
+      <c r="D4">
+        <v>49.8</v>
+      </c>
+      <c r="E4">
+        <v>49.8</v>
+      </c>
+      <c r="F4">
+        <v>49.9</v>
+      </c>
+      <c r="G4">
+        <v>49.9</v>
+      </c>
+      <c r="H4">
+        <v>50.1</v>
+      </c>
+      <c r="I4">
+        <v>50.1</v>
+      </c>
+      <c r="J4">
+        <v>50.2</v>
+      </c>
+      <c r="K4">
+        <v>50.1</v>
+      </c>
+      <c r="L4">
+        <v>50</v>
+      </c>
+      <c r="M4">
+        <v>50</v>
+      </c>
+      <c r="N4">
+        <v>49.8</v>
+      </c>
+      <c r="O4">
         <v>48.9</v>
       </c>
-      <c r="D4">
-        <v>49.6</v>
-      </c>
-      <c r="E4">
-        <v>51</v>
-      </c>
-      <c r="F4">
-        <v>52.90000000000001</v>
-      </c>
-      <c r="G4">
-        <v>50.4</v>
-      </c>
-      <c r="H4">
-        <v>49.4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="P4">
+        <v>49.3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>29.9</v>
+        <v>12.5</v>
       </c>
       <c r="C5">
-        <v>32.9</v>
+        <v>12.5</v>
       </c>
       <c r="D5">
-        <v>43.2</v>
+        <v>12.3</v>
       </c>
       <c r="E5">
-        <v>54.90000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="F5">
-        <v>46.3</v>
+        <v>12.2</v>
       </c>
       <c r="G5">
-        <v>49.4</v>
+        <v>11.7</v>
       </c>
       <c r="H5">
-        <v>51.7</v>
+        <v>12.7</v>
+      </c>
+      <c r="I5">
+        <v>13.8</v>
+      </c>
+      <c r="J5">
+        <v>16.4</v>
+      </c>
+      <c r="K5">
+        <v>24.8</v>
+      </c>
+      <c r="L5">
+        <v>33.8</v>
+      </c>
+      <c r="M5">
+        <v>40.1</v>
+      </c>
+      <c r="N5">
+        <v>50.8</v>
+      </c>
+      <c r="O5">
+        <v>46.9</v>
+      </c>
+      <c r="P5">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:H5">
+  <conditionalFormatting sqref="B2:P5">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -672,13 +912,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="8" width="4.7109375" customWidth="1"/>
+    <col min="2" max="16" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -703,113 +943,233 @@
       <c r="H1">
         <v>16</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1">
+        <v>20</v>
+      </c>
+      <c r="J1">
+        <v>32</v>
+      </c>
+      <c r="K1">
+        <v>64</v>
+      </c>
+      <c r="L1">
+        <v>100</v>
+      </c>
+      <c r="M1">
+        <v>128</v>
+      </c>
+      <c r="N1">
+        <v>256</v>
+      </c>
+      <c r="O1">
+        <v>512</v>
+      </c>
+      <c r="P1">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>15.3</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>35.09999999999999</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>41.9</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0.1</v>
+      </c>
+      <c r="K2">
+        <v>8.6</v>
+      </c>
+      <c r="L2">
+        <v>18.2</v>
+      </c>
+      <c r="M2">
+        <v>19.7</v>
+      </c>
+      <c r="N2">
+        <v>44.2</v>
+      </c>
+      <c r="O2">
+        <v>49.3</v>
+      </c>
+      <c r="P2">
         <v>48.9</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>21.5</v>
+        <v>10.9</v>
       </c>
       <c r="C3">
-        <v>21.2</v>
+        <v>10.8</v>
       </c>
       <c r="D3">
-        <v>20.3</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>22.4</v>
+        <v>11.1</v>
       </c>
       <c r="F3">
-        <v>24.7</v>
+        <v>11.3</v>
       </c>
       <c r="G3">
-        <v>27</v>
+        <v>11.5</v>
       </c>
       <c r="H3">
-        <v>33.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>12.2</v>
+      </c>
+      <c r="I3">
+        <v>12.2</v>
+      </c>
+      <c r="J3">
+        <v>12.7</v>
+      </c>
+      <c r="K3">
+        <v>15.2</v>
+      </c>
+      <c r="L3">
+        <v>17.3</v>
+      </c>
+      <c r="M3">
+        <v>19.4</v>
+      </c>
+      <c r="N3">
+        <v>27.3</v>
+      </c>
+      <c r="O3">
+        <v>41.7</v>
+      </c>
+      <c r="P3">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="C4">
-        <v>25.8</v>
+        <v>23.9</v>
       </c>
       <c r="D4">
+        <v>23.9</v>
+      </c>
+      <c r="E4">
+        <v>23.9</v>
+      </c>
+      <c r="F4">
+        <v>24</v>
+      </c>
+      <c r="G4">
+        <v>23.7</v>
+      </c>
+      <c r="H4">
+        <v>23.3</v>
+      </c>
+      <c r="I4">
+        <v>23.6</v>
+      </c>
+      <c r="J4">
+        <v>24</v>
+      </c>
+      <c r="K4">
+        <v>23.6</v>
+      </c>
+      <c r="L4">
+        <v>24.6</v>
+      </c>
+      <c r="M4">
+        <v>25</v>
+      </c>
+      <c r="N4">
         <v>25.9</v>
       </c>
-      <c r="E4">
-        <v>24.6</v>
-      </c>
-      <c r="F4">
-        <v>25.4</v>
-      </c>
-      <c r="G4">
-        <v>25.3</v>
-      </c>
-      <c r="H4">
-        <v>24.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="O4">
+        <v>28.3</v>
+      </c>
+      <c r="P4">
+        <v>29.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>0.4</v>
       </c>
-      <c r="C5">
-        <v>14.1</v>
-      </c>
-      <c r="D5">
-        <v>25.2</v>
-      </c>
-      <c r="E5">
-        <v>39.3</v>
-      </c>
-      <c r="F5">
-        <v>50.9</v>
-      </c>
-      <c r="G5">
-        <v>51.2</v>
-      </c>
-      <c r="H5">
-        <v>49.6</v>
+      <c r="J5">
+        <v>2.1</v>
+      </c>
+      <c r="K5">
+        <v>11.3</v>
+      </c>
+      <c r="L5">
+        <v>14.5</v>
+      </c>
+      <c r="M5">
+        <v>15</v>
+      </c>
+      <c r="N5">
+        <v>29.1</v>
+      </c>
+      <c r="O5">
+        <v>45</v>
+      </c>
+      <c r="P5">
+        <v>51.9</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:H5">
+  <conditionalFormatting sqref="B2:P5">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/mlp-exp/alpha_sweep_results.xlsx
+++ b/mlp-exp/alpha_sweep_results.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sign_Accuracy" sheetId="1" r:id="rId1"/>
-    <sheet name="Parity_Accuracy" sheetId="2" r:id="rId2"/>
+    <sheet name="Subset_Accuracy" sheetId="2" r:id="rId2"/>
     <sheet name="Total_Accuracy" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -423,49 +423,49 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K2">
-        <v>11.9</v>
+        <v>25.2</v>
       </c>
       <c r="L2">
-        <v>32.4</v>
+        <v>27.5</v>
       </c>
       <c r="M2">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="N2">
-        <v>89.8</v>
+        <v>38.1</v>
       </c>
       <c r="O2">
-        <v>100</v>
+        <v>57.3</v>
       </c>
       <c r="P2">
-        <v>100</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -473,49 +473,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>21.2</v>
+        <v>32.2</v>
       </c>
       <c r="C3">
-        <v>21.2</v>
+        <v>32.2</v>
       </c>
       <c r="D3">
-        <v>21.3</v>
+        <v>32.2</v>
       </c>
       <c r="E3">
-        <v>21.3</v>
+        <v>32.2</v>
       </c>
       <c r="F3">
-        <v>21.3</v>
+        <v>32.3</v>
       </c>
       <c r="G3">
-        <v>21.5</v>
+        <v>32.7</v>
       </c>
       <c r="H3">
-        <v>22.1</v>
+        <v>33.4</v>
       </c>
       <c r="I3">
-        <v>22.4</v>
+        <v>33.5</v>
       </c>
       <c r="J3">
-        <v>23.6</v>
+        <v>34.3</v>
       </c>
       <c r="K3">
-        <v>28.7</v>
+        <v>36.5</v>
       </c>
       <c r="L3">
-        <v>32.5</v>
+        <v>39.5</v>
       </c>
       <c r="M3">
-        <v>36.8</v>
+        <v>40.5</v>
       </c>
       <c r="N3">
-        <v>54.50000000000001</v>
+        <v>50.3</v>
       </c>
       <c r="O3">
-        <v>81.5</v>
+        <v>68.60000000000001</v>
       </c>
       <c r="P3">
-        <v>99.40000000000001</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -523,46 +523,46 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>50.7</v>
+        <v>36.7</v>
       </c>
       <c r="C4">
-        <v>50.7</v>
+        <v>36.7</v>
       </c>
       <c r="D4">
-        <v>50.7</v>
+        <v>36.7</v>
       </c>
       <c r="E4">
-        <v>50.7</v>
+        <v>36.7</v>
       </c>
       <c r="F4">
-        <v>50.7</v>
+        <v>36.7</v>
       </c>
       <c r="G4">
-        <v>50.7</v>
+        <v>36.7</v>
       </c>
       <c r="H4">
-        <v>50.7</v>
+        <v>36.7</v>
       </c>
       <c r="I4">
-        <v>50.7</v>
+        <v>36.7</v>
       </c>
       <c r="J4">
-        <v>50.7</v>
+        <v>36.8</v>
       </c>
       <c r="K4">
-        <v>50.9</v>
+        <v>37.3</v>
       </c>
       <c r="L4">
-        <v>50.9</v>
+        <v>38.2</v>
       </c>
       <c r="M4">
-        <v>51</v>
+        <v>38.6</v>
       </c>
       <c r="N4">
-        <v>51.8</v>
+        <v>40.8</v>
       </c>
       <c r="O4">
-        <v>53.5</v>
+        <v>45.9</v>
       </c>
       <c r="P4">
         <v>56.8</v>
@@ -573,49 +573,49 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>1.1</v>
+        <v>25</v>
       </c>
       <c r="C5">
-        <v>1.2</v>
+        <v>25.1</v>
       </c>
       <c r="D5">
-        <v>1.2</v>
+        <v>25.1</v>
       </c>
       <c r="E5">
-        <v>1.2</v>
+        <v>25.3</v>
       </c>
       <c r="F5">
-        <v>1.5</v>
+        <v>25.4</v>
       </c>
       <c r="G5">
-        <v>2.9</v>
+        <v>25.5</v>
       </c>
       <c r="H5">
-        <v>4.2</v>
+        <v>25.9</v>
       </c>
       <c r="I5">
-        <v>5.4</v>
+        <v>26</v>
       </c>
       <c r="J5">
-        <v>8.1</v>
+        <v>26.5</v>
       </c>
       <c r="K5">
-        <v>16.1</v>
+        <v>27.8</v>
       </c>
       <c r="L5">
-        <v>26.1</v>
+        <v>30.4</v>
       </c>
       <c r="M5">
-        <v>33.2</v>
+        <v>31.8</v>
       </c>
       <c r="N5">
-        <v>59.5</v>
+        <v>39.1</v>
       </c>
       <c r="O5">
-        <v>91.60000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="P5">
-        <v>100</v>
+        <v>97.2</v>
       </c>
     </row>
   </sheetData>
@@ -698,49 +698,49 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.5</v>
+        <v>47.3</v>
       </c>
       <c r="C2">
-        <v>0.5</v>
+        <v>47.2</v>
       </c>
       <c r="D2">
-        <v>0.5</v>
+        <v>47.2</v>
       </c>
       <c r="E2">
-        <v>0.5</v>
+        <v>47.2</v>
       </c>
       <c r="F2">
-        <v>0.5</v>
+        <v>47.2</v>
       </c>
       <c r="G2">
-        <v>0.6</v>
+        <v>47.2</v>
       </c>
       <c r="H2">
-        <v>0.8999999999999999</v>
+        <v>47.09999999999999</v>
       </c>
       <c r="I2">
-        <v>0.7000000000000001</v>
+        <v>47.2</v>
       </c>
       <c r="J2">
-        <v>1.7</v>
+        <v>46.7</v>
       </c>
       <c r="K2">
-        <v>7.9</v>
+        <v>46.2</v>
       </c>
       <c r="L2">
-        <v>21.3</v>
+        <v>45.4</v>
       </c>
       <c r="M2">
-        <v>31.9</v>
+        <v>45.2</v>
       </c>
       <c r="N2">
-        <v>50</v>
+        <v>43.4</v>
       </c>
       <c r="O2">
-        <v>46.5</v>
+        <v>35.3</v>
       </c>
       <c r="P2">
-        <v>48.1</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -748,49 +748,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>49.7</v>
+        <v>95</v>
       </c>
       <c r="C3">
-        <v>49.6</v>
+        <v>95</v>
       </c>
       <c r="D3">
-        <v>49.7</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="E3">
-        <v>49.7</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="F3">
-        <v>50</v>
+        <v>94.89999999999999</v>
       </c>
       <c r="G3">
-        <v>50.1</v>
+        <v>94.8</v>
       </c>
       <c r="H3">
-        <v>50.7</v>
+        <v>94.8</v>
       </c>
       <c r="I3">
-        <v>50.6</v>
+        <v>94.8</v>
       </c>
       <c r="J3">
-        <v>51.2</v>
+        <v>94.69999999999999</v>
       </c>
       <c r="K3">
-        <v>51.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="L3">
-        <v>53.3</v>
+        <v>94.5</v>
       </c>
       <c r="M3">
-        <v>53.1</v>
+        <v>94</v>
       </c>
       <c r="N3">
-        <v>53</v>
+        <v>93.30000000000001</v>
       </c>
       <c r="O3">
-        <v>53.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="P3">
-        <v>52.8</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -798,49 +798,49 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>49.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="C4">
-        <v>49.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D4">
-        <v>49.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="E4">
-        <v>49.8</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="F4">
-        <v>49.9</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="G4">
-        <v>49.9</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="H4">
-        <v>50.1</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="I4">
-        <v>50.1</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="J4">
-        <v>50.2</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="K4">
-        <v>50.1</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="L4">
-        <v>50</v>
+        <v>99.5</v>
       </c>
       <c r="M4">
-        <v>50</v>
+        <v>99.5</v>
       </c>
       <c r="N4">
-        <v>49.8</v>
+        <v>99.5</v>
       </c>
       <c r="O4">
-        <v>48.9</v>
+        <v>99.7</v>
       </c>
       <c r="P4">
-        <v>49.3</v>
+        <v>99.90000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -848,49 +848,49 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>12.5</v>
+        <v>50.3</v>
       </c>
       <c r="C5">
-        <v>12.5</v>
+        <v>50.3</v>
       </c>
       <c r="D5">
-        <v>12.3</v>
+        <v>50.3</v>
       </c>
       <c r="E5">
-        <v>12.2</v>
+        <v>50.3</v>
       </c>
       <c r="F5">
-        <v>12.2</v>
+        <v>50.2</v>
       </c>
       <c r="G5">
-        <v>11.7</v>
+        <v>50.2</v>
       </c>
       <c r="H5">
-        <v>12.7</v>
+        <v>50</v>
       </c>
       <c r="I5">
-        <v>13.8</v>
+        <v>50</v>
       </c>
       <c r="J5">
-        <v>16.4</v>
+        <v>49.9</v>
       </c>
       <c r="K5">
-        <v>24.8</v>
+        <v>49</v>
       </c>
       <c r="L5">
-        <v>33.8</v>
+        <v>47.7</v>
       </c>
       <c r="M5">
-        <v>40.1</v>
+        <v>47.09999999999999</v>
       </c>
       <c r="N5">
-        <v>50.8</v>
+        <v>43.4</v>
       </c>
       <c r="O5">
-        <v>46.9</v>
+        <v>36.8</v>
       </c>
       <c r="P5">
-        <v>46</v>
+        <v>29.9</v>
       </c>
     </row>
   </sheetData>
@@ -973,49 +973,49 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>10.6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>10.8</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="J2">
-        <v>0.1</v>
+        <v>10.8</v>
       </c>
       <c r="K2">
-        <v>8.6</v>
+        <v>10.3</v>
       </c>
       <c r="L2">
-        <v>18.2</v>
+        <v>11.6</v>
       </c>
       <c r="M2">
-        <v>19.7</v>
+        <v>13.4</v>
       </c>
       <c r="N2">
-        <v>44.2</v>
+        <v>16.5</v>
       </c>
       <c r="O2">
-        <v>49.3</v>
+        <v>29.4</v>
       </c>
       <c r="P2">
-        <v>48.9</v>
+        <v>25.3</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1023,49 +1023,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>10.9</v>
+        <v>31.5</v>
       </c>
       <c r="C3">
-        <v>10.8</v>
+        <v>31.5</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>31.5</v>
       </c>
       <c r="E3">
-        <v>11.1</v>
+        <v>31.4</v>
       </c>
       <c r="F3">
-        <v>11.3</v>
+        <v>31.5</v>
       </c>
       <c r="G3">
-        <v>11.5</v>
+        <v>31.8</v>
       </c>
       <c r="H3">
-        <v>12.2</v>
+        <v>32</v>
       </c>
       <c r="I3">
-        <v>12.2</v>
+        <v>32.3</v>
       </c>
       <c r="J3">
-        <v>12.7</v>
+        <v>32.7</v>
       </c>
       <c r="K3">
-        <v>15.2</v>
+        <v>35</v>
       </c>
       <c r="L3">
-        <v>17.3</v>
+        <v>36.9</v>
       </c>
       <c r="M3">
-        <v>19.4</v>
+        <v>37.8</v>
       </c>
       <c r="N3">
-        <v>27.3</v>
+        <v>44.7</v>
       </c>
       <c r="O3">
-        <v>41.7</v>
+        <v>57.2</v>
       </c>
       <c r="P3">
-        <v>52.5</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1073,49 +1073,49 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>23.9</v>
+        <v>36.4</v>
       </c>
       <c r="C4">
-        <v>23.9</v>
+        <v>36.4</v>
       </c>
       <c r="D4">
-        <v>23.9</v>
+        <v>36.4</v>
       </c>
       <c r="E4">
-        <v>23.9</v>
+        <v>36.4</v>
       </c>
       <c r="F4">
-        <v>24</v>
+        <v>36.4</v>
       </c>
       <c r="G4">
-        <v>23.7</v>
+        <v>36.4</v>
       </c>
       <c r="H4">
-        <v>23.3</v>
+        <v>36.4</v>
       </c>
       <c r="I4">
-        <v>23.6</v>
+        <v>36.4</v>
       </c>
       <c r="J4">
-        <v>24</v>
+        <v>36.4</v>
       </c>
       <c r="K4">
-        <v>23.6</v>
+        <v>36.5</v>
       </c>
       <c r="L4">
-        <v>24.6</v>
+        <v>37</v>
       </c>
       <c r="M4">
-        <v>25</v>
+        <v>37.4</v>
       </c>
       <c r="N4">
-        <v>25.9</v>
+        <v>38.8</v>
       </c>
       <c r="O4">
-        <v>28.3</v>
+        <v>42.1</v>
       </c>
       <c r="P4">
-        <v>29.1</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1123,49 +1123,49 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>11.7</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>11.9</v>
       </c>
       <c r="I5">
-        <v>0.4</v>
+        <v>12.2</v>
       </c>
       <c r="J5">
-        <v>2.1</v>
+        <v>12.4</v>
       </c>
       <c r="K5">
-        <v>11.3</v>
+        <v>12.1</v>
       </c>
       <c r="L5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="M5">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="N5">
-        <v>29.1</v>
+        <v>18.3</v>
       </c>
       <c r="O5">
-        <v>45</v>
+        <v>32.3</v>
       </c>
       <c r="P5">
-        <v>51.9</v>
+        <v>24.6</v>
       </c>
     </row>
   </sheetData>

--- a/mlp-exp/alpha_sweep_results.xlsx
+++ b/mlp-exp/alpha_sweep_results.xlsx
@@ -450,22 +450,22 @@
         <v>25</v>
       </c>
       <c r="K2">
-        <v>25.2</v>
+        <v>26.5</v>
       </c>
       <c r="L2">
-        <v>27.5</v>
+        <v>29.5</v>
       </c>
       <c r="M2">
-        <v>29</v>
+        <v>30.8</v>
       </c>
       <c r="N2">
-        <v>38.1</v>
+        <v>39.4</v>
       </c>
       <c r="O2">
-        <v>57.3</v>
+        <v>61.6</v>
       </c>
       <c r="P2">
-        <v>97.3</v>
+        <v>99.3</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -473,49 +473,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>32.2</v>
+        <v>35.7</v>
       </c>
       <c r="C3">
-        <v>32.2</v>
+        <v>35.7</v>
       </c>
       <c r="D3">
-        <v>32.2</v>
+        <v>35.9</v>
       </c>
       <c r="E3">
-        <v>32.2</v>
+        <v>35.9</v>
       </c>
       <c r="F3">
-        <v>32.3</v>
+        <v>36.3</v>
       </c>
       <c r="G3">
-        <v>32.7</v>
+        <v>36.6</v>
       </c>
       <c r="H3">
-        <v>33.4</v>
+        <v>37.1</v>
       </c>
       <c r="I3">
-        <v>33.5</v>
+        <v>37.3</v>
       </c>
       <c r="J3">
-        <v>34.3</v>
+        <v>38.1</v>
       </c>
       <c r="K3">
-        <v>36.5</v>
+        <v>40.5</v>
       </c>
       <c r="L3">
-        <v>39.5</v>
+        <v>42.8</v>
       </c>
       <c r="M3">
-        <v>40.5</v>
+        <v>45.3</v>
       </c>
       <c r="N3">
-        <v>50.3</v>
+        <v>55.3</v>
       </c>
       <c r="O3">
-        <v>68.60000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="P3">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -523,49 +523,49 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>36.7</v>
+        <v>25</v>
       </c>
       <c r="C4">
-        <v>36.7</v>
+        <v>25</v>
       </c>
       <c r="D4">
-        <v>36.7</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>36.7</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>36.7</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>36.7</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>36.7</v>
+        <v>25</v>
       </c>
       <c r="I4">
-        <v>36.7</v>
+        <v>25</v>
       </c>
       <c r="J4">
-        <v>36.8</v>
+        <v>25</v>
       </c>
       <c r="K4">
-        <v>37.3</v>
+        <v>25</v>
       </c>
       <c r="L4">
-        <v>38.2</v>
+        <v>25</v>
       </c>
       <c r="M4">
-        <v>38.6</v>
+        <v>25</v>
       </c>
       <c r="N4">
-        <v>40.8</v>
+        <v>25</v>
       </c>
       <c r="O4">
-        <v>45.9</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>56.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -573,49 +573,49 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>25</v>
+        <v>24.6</v>
       </c>
       <c r="C5">
+        <v>24.6</v>
+      </c>
+      <c r="D5">
+        <v>24.6</v>
+      </c>
+      <c r="E5">
+        <v>24.6</v>
+      </c>
+      <c r="F5">
+        <v>24.9</v>
+      </c>
+      <c r="G5">
         <v>25.1</v>
       </c>
-      <c r="D5">
-        <v>25.1</v>
-      </c>
-      <c r="E5">
-        <v>25.3</v>
-      </c>
-      <c r="F5">
-        <v>25.4</v>
-      </c>
-      <c r="G5">
-        <v>25.5</v>
-      </c>
       <c r="H5">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="I5">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="J5">
-        <v>26.5</v>
+        <v>27.1</v>
       </c>
       <c r="K5">
-        <v>27.8</v>
+        <v>28.7</v>
       </c>
       <c r="L5">
-        <v>30.4</v>
+        <v>31</v>
       </c>
       <c r="M5">
-        <v>31.8</v>
+        <v>33.4</v>
       </c>
       <c r="N5">
-        <v>39.1</v>
+        <v>41</v>
       </c>
       <c r="O5">
-        <v>60.9</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="P5">
-        <v>97.2</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -698,49 +698,49 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>47.3</v>
+        <v>49.6</v>
       </c>
       <c r="C2">
-        <v>47.2</v>
+        <v>49.6</v>
       </c>
       <c r="D2">
-        <v>47.2</v>
+        <v>49.6</v>
       </c>
       <c r="E2">
-        <v>47.2</v>
+        <v>49.6</v>
       </c>
       <c r="F2">
-        <v>47.2</v>
+        <v>49.5</v>
       </c>
       <c r="G2">
-        <v>47.2</v>
+        <v>49.3</v>
       </c>
       <c r="H2">
-        <v>47.09999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="I2">
-        <v>47.2</v>
+        <v>48.4</v>
       </c>
       <c r="J2">
-        <v>46.7</v>
+        <v>48.1</v>
       </c>
       <c r="K2">
-        <v>46.2</v>
+        <v>47</v>
       </c>
       <c r="L2">
-        <v>45.4</v>
+        <v>46.5</v>
       </c>
       <c r="M2">
-        <v>45.2</v>
+        <v>46.3</v>
       </c>
       <c r="N2">
-        <v>43.4</v>
+        <v>44.1</v>
       </c>
       <c r="O2">
-        <v>35.3</v>
+        <v>37.9</v>
       </c>
       <c r="P2">
-        <v>24.9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -748,49 +748,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C3">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D3">
-        <v>94.89999999999999</v>
+        <v>91</v>
       </c>
       <c r="E3">
-        <v>94.89999999999999</v>
+        <v>91</v>
       </c>
       <c r="F3">
-        <v>94.89999999999999</v>
+        <v>91</v>
       </c>
       <c r="G3">
-        <v>94.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H3">
-        <v>94.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I3">
-        <v>94.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="J3">
-        <v>94.69999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K3">
-        <v>94.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="L3">
-        <v>94.5</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M3">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="N3">
-        <v>93.30000000000001</v>
+        <v>91</v>
       </c>
       <c r="O3">
-        <v>91.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P3">
-        <v>84.8</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -798,49 +798,49 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="C4">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D4">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="E4">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I4">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>99.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="L4">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="M4">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="N4">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="O4">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -848,49 +848,49 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>50.3</v>
+        <v>49.8</v>
       </c>
       <c r="C5">
-        <v>50.3</v>
+        <v>49.8</v>
       </c>
       <c r="D5">
-        <v>50.3</v>
+        <v>49.8</v>
       </c>
       <c r="E5">
-        <v>50.3</v>
+        <v>49.8</v>
       </c>
       <c r="F5">
-        <v>50.2</v>
+        <v>49.8</v>
       </c>
       <c r="G5">
-        <v>50.2</v>
+        <v>49.7</v>
       </c>
       <c r="H5">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="I5">
-        <v>50</v>
+        <v>49.4</v>
       </c>
       <c r="J5">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="K5">
-        <v>49</v>
+        <v>48.4</v>
       </c>
       <c r="L5">
-        <v>47.7</v>
+        <v>47.59999999999999</v>
       </c>
       <c r="M5">
-        <v>47.09999999999999</v>
+        <v>47.2</v>
       </c>
       <c r="N5">
-        <v>43.4</v>
+        <v>44.4</v>
       </c>
       <c r="O5">
-        <v>36.8</v>
+        <v>38.7</v>
       </c>
       <c r="P5">
-        <v>29.9</v>
+        <v>30.2</v>
       </c>
     </row>
   </sheetData>
@@ -973,49 +973,49 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="C2">
-        <v>10.5</v>
+        <v>10.6</v>
       </c>
       <c r="D2">
         <v>10.6</v>
       </c>
       <c r="E2">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="F2">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="G2">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="H2">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="I2">
-        <v>10.7</v>
+        <v>10.4</v>
       </c>
       <c r="J2">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="K2">
-        <v>10.3</v>
+        <v>11.4</v>
       </c>
       <c r="L2">
-        <v>11.6</v>
+        <v>12.5</v>
       </c>
       <c r="M2">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="N2">
-        <v>16.5</v>
+        <v>18.1</v>
       </c>
       <c r="O2">
-        <v>29.4</v>
+        <v>26</v>
       </c>
       <c r="P2">
-        <v>25.3</v>
+        <v>28.4</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -1023,49 +1023,49 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>31.5</v>
+        <v>35.09999999999999</v>
       </c>
       <c r="C3">
-        <v>31.5</v>
+        <v>35.09999999999999</v>
       </c>
       <c r="D3">
-        <v>31.5</v>
+        <v>35.3</v>
       </c>
       <c r="E3">
-        <v>31.4</v>
+        <v>35.3</v>
       </c>
       <c r="F3">
-        <v>31.5</v>
+        <v>35.7</v>
       </c>
       <c r="G3">
-        <v>31.8</v>
+        <v>35.9</v>
       </c>
       <c r="H3">
-        <v>32</v>
+        <v>36.3</v>
       </c>
       <c r="I3">
-        <v>32.3</v>
+        <v>36.5</v>
       </c>
       <c r="J3">
-        <v>32.7</v>
+        <v>37.3</v>
       </c>
       <c r="K3">
-        <v>35</v>
+        <v>39.5</v>
       </c>
       <c r="L3">
-        <v>36.9</v>
+        <v>41.9</v>
       </c>
       <c r="M3">
-        <v>37.8</v>
+        <v>43.7</v>
       </c>
       <c r="N3">
-        <v>44.7</v>
+        <v>52.7</v>
       </c>
       <c r="O3">
-        <v>57.2</v>
+        <v>58.8</v>
       </c>
       <c r="P3">
-        <v>42.1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -1073,49 +1073,49 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="C4">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="D4">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="E4">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="I4">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="J4">
-        <v>36.4</v>
+        <v>25</v>
       </c>
       <c r="K4">
-        <v>36.5</v>
+        <v>25</v>
       </c>
       <c r="L4">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="M4">
-        <v>37.4</v>
+        <v>25</v>
       </c>
       <c r="N4">
-        <v>38.8</v>
+        <v>25</v>
       </c>
       <c r="O4">
-        <v>42.1</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>49.4</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -1123,49 +1123,49 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="C5">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="D5">
-        <v>11.4</v>
+        <v>11.9</v>
       </c>
       <c r="E5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="F5">
-        <v>11.5</v>
+        <v>12.3</v>
       </c>
       <c r="G5">
-        <v>11.7</v>
+        <v>12.3</v>
       </c>
       <c r="H5">
-        <v>11.9</v>
+        <v>12.4</v>
       </c>
       <c r="I5">
-        <v>12.2</v>
+        <v>12.7</v>
       </c>
       <c r="J5">
-        <v>12.4</v>
+        <v>13.2</v>
       </c>
       <c r="K5">
-        <v>12.1</v>
+        <v>13.5</v>
       </c>
       <c r="L5">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="M5">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="N5">
-        <v>18.3</v>
+        <v>18.7</v>
       </c>
       <c r="O5">
-        <v>32.3</v>
+        <v>27.8</v>
       </c>
       <c r="P5">
-        <v>24.6</v>
+        <v>29.6</v>
       </c>
     </row>
   </sheetData>
